--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7370D995-9AC5-42ED-8C5D-FF16B35400B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F834A-02FA-487C-936E-AED728F05C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -29,16 +29,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -122,35 +123,39 @@
     <t>https://dashboard.tacindex.com/dashboard</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>UTC+1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -172,7 +177,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -189,7 +194,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -233,7 +238,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -253,34 +258,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -298,7 +303,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1640,6 +1645,9 @@
                 <c:pt idx="429">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4274,6 +4282,9 @@
                 <c:pt idx="429">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6908,6 +6919,9 @@
                 <c:pt idx="429">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9542,6 +9556,9 @@
                 <c:pt idx="429">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12175,6 +12192,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14811,6 +14831,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17461,6 +17484,9 @@
                 </c:pt>
                 <c:pt idx="429">
                   <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>46118</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19003,7 +19029,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19011,6 +19036,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19905,21 +19931,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K432"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K433"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" customHeight="1">
+    <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
@@ -19954,7 +19980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="14"/>
@@ -19981,7 +20007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <v>43100</v>
       </c>
@@ -20016,7 +20042,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>43107</v>
       </c>
@@ -20051,7 +20077,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>43114</v>
       </c>
@@ -20086,7 +20112,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>43121</v>
       </c>
@@ -20121,7 +20147,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>43128</v>
       </c>
@@ -20156,7 +20182,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>43135</v>
       </c>
@@ -20191,7 +20217,7 @@
         <v>2899</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>43142</v>
       </c>
@@ -20226,7 +20252,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>43149</v>
       </c>
@@ -20261,7 +20287,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>43156</v>
       </c>
@@ -20296,7 +20322,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>43163</v>
       </c>
@@ -20331,7 +20357,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>43170</v>
       </c>
@@ -20366,7 +20392,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>43177</v>
       </c>
@@ -20401,7 +20427,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>43184</v>
       </c>
@@ -20436,7 +20462,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>43191</v>
       </c>
@@ -20471,7 +20497,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>43198</v>
       </c>
@@ -20506,7 +20532,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>43205</v>
       </c>
@@ -20541,7 +20567,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>43212</v>
       </c>
@@ -20576,7 +20602,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
         <v>43219</v>
       </c>
@@ -20611,7 +20637,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="10">
         <v>43226</v>
       </c>
@@ -20646,7 +20672,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
         <v>43233</v>
       </c>
@@ -20681,7 +20707,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
         <v>43240</v>
       </c>
@@ -20716,7 +20742,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
         <v>43247</v>
       </c>
@@ -20751,7 +20777,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="10">
         <v>43254</v>
       </c>
@@ -20786,7 +20812,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>43261</v>
       </c>
@@ -20821,7 +20847,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>43268</v>
       </c>
@@ -20856,7 +20882,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
         <v>43275</v>
       </c>
@@ -20891,7 +20917,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>43282</v>
       </c>
@@ -20926,7 +20952,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>43289</v>
       </c>
@@ -20961,7 +20987,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>43296</v>
       </c>
@@ -20996,7 +21022,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>43303</v>
       </c>
@@ -21031,7 +21057,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>43310</v>
       </c>
@@ -21066,7 +21092,7 @@
         <v>3174</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>43317</v>
       </c>
@@ -21101,7 +21127,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>43324</v>
       </c>
@@ -21136,7 +21162,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>43331</v>
       </c>
@@ -21171,7 +21197,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>43338</v>
       </c>
@@ -21206,7 +21232,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>43345</v>
       </c>
@@ -21241,7 +21267,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>43352</v>
       </c>
@@ -21276,7 +21302,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>43359</v>
       </c>
@@ -21311,7 +21337,7 @@
         <v>3254</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>43366</v>
       </c>
@@ -21346,7 +21372,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>43373</v>
       </c>
@@ -21381,7 +21407,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>43380</v>
       </c>
@@ -21416,7 +21442,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>43387</v>
       </c>
@@ -21451,7 +21477,7 @@
         <v>3296</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>43394</v>
       </c>
@@ -21486,7 +21512,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>43401</v>
       </c>
@@ -21521,7 +21547,7 @@
         <v>3658</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>43408</v>
       </c>
@@ -21556,7 +21582,7 @@
         <v>3881</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>43415</v>
       </c>
@@ -21591,7 +21617,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>43422</v>
       </c>
@@ -21626,7 +21652,7 @@
         <v>3795</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>43429</v>
       </c>
@@ -21661,7 +21687,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>43436</v>
       </c>
@@ -21696,7 +21722,7 @@
         <v>3542</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>43443</v>
       </c>
@@ -21731,7 +21757,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>43450</v>
       </c>
@@ -21766,7 +21792,7 @@
         <v>3495</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
         <v>43457</v>
       </c>
@@ -21801,7 +21827,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
         <v>43464</v>
       </c>
@@ -21836,7 +21862,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
         <v>43471</v>
       </c>
@@ -21871,7 +21897,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
         <v>43478</v>
       </c>
@@ -21906,7 +21932,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
         <v>43485</v>
       </c>
@@ -21941,7 +21967,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="10">
         <v>43492</v>
       </c>
@@ -21976,7 +22002,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
         <v>43499</v>
       </c>
@@ -22011,7 +22037,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="10">
         <v>43506</v>
       </c>
@@ -22046,7 +22072,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
         <v>43513</v>
       </c>
@@ -22081,7 +22107,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
         <v>43520</v>
       </c>
@@ -22116,7 +22142,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
         <v>43527</v>
       </c>
@@ -22151,7 +22177,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="10">
         <v>43534</v>
       </c>
@@ -22186,7 +22212,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="10">
         <v>43541</v>
       </c>
@@ -22221,7 +22247,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
         <v>43548</v>
       </c>
@@ -22256,7 +22282,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="10">
         <v>43555</v>
       </c>
@@ -22291,7 +22317,7 @@
         <v>2977</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="10">
         <v>43562</v>
       </c>
@@ -22326,7 +22352,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="10">
         <v>43569</v>
       </c>
@@ -22361,7 +22387,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="10">
         <v>43576</v>
       </c>
@@ -22396,7 +22422,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="10">
         <v>43583</v>
       </c>
@@ -22431,7 +22457,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="10">
         <v>43590</v>
       </c>
@@ -22466,7 +22492,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="10">
         <v>43597</v>
       </c>
@@ -22501,7 +22527,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="10">
         <v>43604</v>
       </c>
@@ -22536,7 +22562,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="10">
         <v>43611</v>
       </c>
@@ -22571,7 +22597,7 @@
         <v>2788</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="10">
         <v>43618</v>
       </c>
@@ -22606,7 +22632,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="10">
         <v>43625</v>
       </c>
@@ -22641,7 +22667,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="10">
         <v>43632</v>
       </c>
@@ -22676,7 +22702,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="10">
         <v>43639</v>
       </c>
@@ -22711,7 +22737,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="10">
         <v>43646</v>
       </c>
@@ -22746,7 +22772,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="10">
         <v>43653</v>
       </c>
@@ -22781,7 +22807,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="10">
         <v>43660</v>
       </c>
@@ -22816,7 +22842,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
         <v>43667</v>
       </c>
@@ -22851,7 +22877,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="10">
         <v>43674</v>
       </c>
@@ -22886,7 +22912,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="10">
         <v>43681</v>
       </c>
@@ -22921,7 +22947,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="10">
         <v>43688</v>
       </c>
@@ -22956,7 +22982,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="10">
         <v>43695</v>
       </c>
@@ -22991,7 +23017,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="10">
         <v>43702</v>
       </c>
@@ -23026,7 +23052,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="10">
         <v>43709</v>
       </c>
@@ -23061,7 +23087,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="10">
         <v>43716</v>
       </c>
@@ -23096,7 +23122,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="10">
         <v>43723</v>
       </c>
@@ -23131,7 +23157,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="10">
         <v>43730</v>
       </c>
@@ -23166,7 +23192,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="10">
         <v>43737</v>
       </c>
@@ -23201,7 +23227,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="10">
         <v>43744</v>
       </c>
@@ -23236,7 +23262,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="10">
         <v>43751</v>
       </c>
@@ -23271,7 +23297,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <v>43758</v>
       </c>
@@ -23306,7 +23332,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="10">
         <v>43765</v>
       </c>
@@ -23341,7 +23367,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
         <v>43772</v>
       </c>
@@ -23376,7 +23402,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="10">
         <v>43779</v>
       </c>
@@ -23411,7 +23437,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="10">
         <v>43786</v>
       </c>
@@ -23446,7 +23472,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="10">
         <v>43793</v>
       </c>
@@ -23481,7 +23507,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="10">
         <v>43800</v>
       </c>
@@ -23516,7 +23542,7 @@
         <v>3079</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="10">
         <v>43807</v>
       </c>
@@ -23551,7 +23577,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="10">
         <v>43814</v>
       </c>
@@ -23586,7 +23612,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="10">
         <v>43821</v>
       </c>
@@ -23621,7 +23647,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="10">
         <v>43828</v>
       </c>
@@ -23656,7 +23682,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="10">
         <v>43835</v>
       </c>
@@ -23691,7 +23717,7 @@
         <v>2776</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="10">
         <v>43842</v>
       </c>
@@ -23726,7 +23752,7 @@
         <v>2636</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="10">
         <v>43849</v>
       </c>
@@ -23761,7 +23787,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="10">
         <v>43856</v>
       </c>
@@ -23796,7 +23822,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="10">
         <v>43863</v>
       </c>
@@ -23831,7 +23857,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="10">
         <v>43870</v>
       </c>
@@ -23866,7 +23892,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="10">
         <v>43877</v>
       </c>
@@ -23901,7 +23927,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="10">
         <v>43884</v>
       </c>
@@ -23936,7 +23962,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="10">
         <v>43891</v>
       </c>
@@ -23971,7 +23997,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="10">
         <v>43898</v>
       </c>
@@ -24006,7 +24032,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="10">
         <v>43905</v>
       </c>
@@ -24041,7 +24067,7 @@
         <v>3858</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="10">
         <v>43912</v>
       </c>
@@ -24076,7 +24102,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="10">
         <v>43919</v>
       </c>
@@ -24111,7 +24137,7 @@
         <v>5641</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="10">
         <v>43926</v>
       </c>
@@ -24146,7 +24172,7 @@
         <v>6426</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="10">
         <v>43933</v>
       </c>
@@ -24181,7 +24207,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="10">
         <v>43940</v>
       </c>
@@ -24216,7 +24242,7 @@
         <v>7946</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="10">
         <v>43947</v>
       </c>
@@ -24251,7 +24277,7 @@
         <v>8608</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="10">
         <v>43954</v>
       </c>
@@ -24286,7 +24312,7 @@
         <v>9951</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="10">
         <v>43961</v>
       </c>
@@ -24321,7 +24347,7 @@
         <v>10351</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="10">
         <v>43968</v>
       </c>
@@ -24356,7 +24382,7 @@
         <v>11202</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="10">
         <v>43975</v>
       </c>
@@ -24391,7 +24417,7 @@
         <v>9824</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="10">
         <v>43982</v>
       </c>
@@ -24426,7 +24452,7 @@
         <v>7635</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="10">
         <v>43989</v>
       </c>
@@ -24461,7 +24487,7 @@
         <v>5993</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="10">
         <v>43996</v>
       </c>
@@ -24496,7 +24522,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="10">
         <v>44003</v>
       </c>
@@ -24531,7 +24557,7 @@
         <v>4035</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="10">
         <v>44010</v>
       </c>
@@ -24566,7 +24592,7 @@
         <v>3835</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="10">
         <v>44017</v>
       </c>
@@ -24601,7 +24627,7 @@
         <v>3711</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="10">
         <v>44024</v>
       </c>
@@ -24636,7 +24662,7 @@
         <v>3775</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="10">
         <v>44031</v>
       </c>
@@ -24671,7 +24697,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="10">
         <v>44038</v>
       </c>
@@ -24706,7 +24732,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="10">
         <v>44045</v>
       </c>
@@ -24741,7 +24767,7 @@
         <v>4535</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="10">
         <v>44052</v>
       </c>
@@ -24776,7 +24802,7 @@
         <v>4425</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="10">
         <v>44059</v>
       </c>
@@ -24811,7 +24837,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="10">
         <v>44066</v>
       </c>
@@ -24846,7 +24872,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="10">
         <v>44073</v>
       </c>
@@ -24881,7 +24907,7 @@
         <v>4332</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="10">
         <v>44080</v>
       </c>
@@ -24916,7 +24942,7 @@
         <v>4498</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="10">
         <v>44087</v>
       </c>
@@ -24951,7 +24977,7 @@
         <v>4225</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="10">
         <v>44094</v>
       </c>
@@ -24986,7 +25012,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="10">
         <v>44101</v>
       </c>
@@ -25021,7 +25047,7 @@
         <v>4340</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="10">
         <v>44108</v>
       </c>
@@ -25056,7 +25082,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="10">
         <v>44115</v>
       </c>
@@ -25091,7 +25117,7 @@
         <v>4297</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="10">
         <v>44122</v>
       </c>
@@ -25126,7 +25152,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="10">
         <v>44129</v>
       </c>
@@ -25161,7 +25187,7 @@
         <v>5696</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="10">
         <v>44136</v>
       </c>
@@ -25196,7 +25222,7 @@
         <v>6193</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="10">
         <v>44143</v>
       </c>
@@ -25231,7 +25257,7 @@
         <v>6336</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="10">
         <v>44150</v>
       </c>
@@ -25266,7 +25292,7 @@
         <v>6128</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="10">
         <v>44157</v>
       </c>
@@ -25301,7 +25327,7 @@
         <v>5805</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="10">
         <v>44164</v>
       </c>
@@ -25336,7 +25362,7 @@
         <v>6359</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="10">
         <v>44171</v>
       </c>
@@ -25371,7 +25397,7 @@
         <v>6501</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="10">
         <v>44178</v>
       </c>
@@ -25406,7 +25432,7 @@
         <v>6639</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="10">
         <v>44185</v>
       </c>
@@ -25441,7 +25467,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="10">
         <v>44192</v>
       </c>
@@ -25476,7 +25502,7 @@
         <v>6235</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="10">
         <v>44199</v>
       </c>
@@ -25511,7 +25537,7 @@
         <v>6313</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="10">
         <v>44206</v>
       </c>
@@ -25546,7 +25572,7 @@
         <v>5714</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="10">
         <v>44213</v>
       </c>
@@ -25581,7 +25607,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="10">
         <v>44220</v>
       </c>
@@ -25616,7 +25642,7 @@
         <v>4555</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="10">
         <v>44227</v>
       </c>
@@ -25651,7 +25677,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="10">
         <v>44234</v>
       </c>
@@ -25686,7 +25712,7 @@
         <v>5649</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="10">
         <v>44241</v>
       </c>
@@ -25721,7 +25747,7 @@
         <v>6333</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="10">
         <v>44248</v>
       </c>
@@ -25756,7 +25782,7 @@
         <v>4242</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="10">
         <v>44255</v>
       </c>
@@ -25791,7 +25817,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="10">
         <v>44262</v>
       </c>
@@ -25826,7 +25852,7 @@
         <v>4641</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="10">
         <v>44269</v>
       </c>
@@ -25861,7 +25887,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="10">
         <v>44276</v>
       </c>
@@ -25896,7 +25922,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="10">
         <v>44283</v>
       </c>
@@ -25931,7 +25957,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="10">
         <v>44290</v>
       </c>
@@ -25966,7 +25992,7 @@
         <v>5485</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="10">
         <v>44297</v>
       </c>
@@ -26001,7 +26027,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="10">
         <v>44304</v>
       </c>
@@ -26036,7 +26062,7 @@
         <v>5842</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="10">
         <v>44311</v>
       </c>
@@ -26071,7 +26097,7 @@
         <v>6366</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="10">
         <v>44318</v>
       </c>
@@ -26106,7 +26132,7 @@
         <v>6907</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="10">
         <v>44325</v>
       </c>
@@ -26141,7 +26167,7 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="10">
         <v>44332</v>
       </c>
@@ -26176,7 +26202,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="10">
         <v>44339</v>
       </c>
@@ -26211,7 +26237,7 @@
         <v>6452</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="10">
         <v>44346</v>
       </c>
@@ -26246,7 +26272,7 @@
         <v>5834</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="10">
         <v>44353</v>
       </c>
@@ -26281,7 +26307,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="10">
         <v>44360</v>
       </c>
@@ -26316,7 +26342,7 @@
         <v>5443</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="10">
         <v>44367</v>
       </c>
@@ -26351,7 +26377,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="10">
         <v>44374</v>
       </c>
@@ -26386,7 +26412,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="10">
         <v>44381</v>
       </c>
@@ -26421,7 +26447,7 @@
         <v>5338</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="10">
         <v>44388</v>
       </c>
@@ -26456,7 +26482,7 @@
         <v>5987</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="10">
         <v>44395</v>
       </c>
@@ -26491,7 +26517,7 @@
         <v>5801</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="10">
         <v>44402</v>
       </c>
@@ -26526,7 +26552,7 @@
         <v>5421</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="10">
         <v>44409</v>
       </c>
@@ -26561,7 +26587,7 @@
         <v>5883</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="10">
         <v>44416</v>
       </c>
@@ -26596,7 +26622,7 @@
         <v>5967</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="10">
         <v>44423</v>
       </c>
@@ -26631,7 +26657,7 @@
         <v>6015</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="10">
         <v>44430</v>
       </c>
@@ -26666,7 +26692,7 @@
         <v>6147</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="10">
         <v>44437</v>
       </c>
@@ -26701,7 +26727,7 @@
         <v>7552</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="10">
         <v>44444</v>
       </c>
@@ -26736,7 +26762,7 @@
         <v>8099</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="10">
         <v>44451</v>
       </c>
@@ -26771,7 +26797,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="10">
         <v>44458</v>
       </c>
@@ -26806,7 +26832,7 @@
         <v>9021</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="10">
         <v>44465</v>
       </c>
@@ -26841,7 +26867,7 @@
         <v>9364</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="10">
         <v>44472</v>
       </c>
@@ -26876,7 +26902,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="10">
         <v>44479</v>
       </c>
@@ -26911,7 +26937,7 @@
         <v>8936</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="10">
         <v>44486</v>
       </c>
@@ -26946,7 +26972,7 @@
         <v>8252</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="10">
         <v>44493</v>
       </c>
@@ -26981,7 +27007,7 @@
         <v>8513</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="10">
         <v>44500</v>
       </c>
@@ -27016,7 +27042,7 @@
         <v>8569</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="10">
         <v>44507</v>
       </c>
@@ -27051,7 +27077,7 @@
         <v>10146</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="10">
         <v>44514</v>
       </c>
@@ -27086,7 +27112,7 @@
         <v>9833</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="10">
         <v>44521</v>
       </c>
@@ -27121,7 +27147,7 @@
         <v>10713</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="10">
         <v>44528</v>
       </c>
@@ -27156,7 +27182,7 @@
         <v>10672</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="10">
         <v>44535</v>
       </c>
@@ -27191,7 +27217,7 @@
         <v>11408</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="10">
         <v>44542</v>
       </c>
@@ -27226,7 +27252,7 @@
         <v>12068</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="10">
         <v>44549</v>
       </c>
@@ -27261,7 +27287,7 @@
         <v>10758</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="10">
         <v>44556</v>
       </c>
@@ -27296,7 +27322,7 @@
         <v>10247</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="10">
         <v>44563</v>
       </c>
@@ -27331,7 +27357,7 @@
         <v>9786</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="10">
         <v>44570</v>
       </c>
@@ -27366,7 +27392,7 @@
         <v>8461</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="10">
         <v>44577</v>
       </c>
@@ -27401,7 +27427,7 @@
         <v>6933</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="10">
         <v>44584</v>
       </c>
@@ -27436,7 +27462,7 @@
         <v>7524</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="10">
         <v>44591</v>
       </c>
@@ -27471,7 +27497,7 @@
         <v>7909</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="10">
         <v>44598</v>
       </c>
@@ -27506,7 +27532,7 @@
         <v>6947</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="10">
         <v>44605</v>
       </c>
@@ -27541,7 +27567,7 @@
         <v>6615</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="10">
         <v>44612</v>
       </c>
@@ -27576,7 +27602,7 @@
         <v>6659</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="10">
         <v>44619</v>
       </c>
@@ -27611,7 +27637,7 @@
         <v>6470</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="10">
         <v>44626</v>
       </c>
@@ -27646,7 +27672,7 @@
         <v>5896</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="10">
         <v>44633</v>
       </c>
@@ -27681,7 +27707,7 @@
         <v>7688</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="10">
         <v>44640</v>
       </c>
@@ -27716,7 +27742,7 @@
         <v>7591</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="10">
         <v>44647</v>
       </c>
@@ -27751,7 +27777,7 @@
         <v>7550</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="10">
         <v>44654</v>
       </c>
@@ -27786,7 +27812,7 @@
         <v>8345</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="10">
         <v>44661</v>
       </c>
@@ -27821,7 +27847,7 @@
         <v>8476</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="10">
         <v>44668</v>
       </c>
@@ -27856,7 +27882,7 @@
         <v>7813</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="10">
         <v>44675</v>
       </c>
@@ -27891,7 +27917,7 @@
         <v>8281</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="10">
         <v>44682</v>
       </c>
@@ -27926,7 +27952,7 @@
         <v>7753</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="10">
         <v>44689</v>
       </c>
@@ -27961,7 +27987,7 @@
         <v>7190</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="10">
         <v>44696</v>
       </c>
@@ -27996,7 +28022,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="10">
         <v>44703</v>
       </c>
@@ -28031,7 +28057,7 @@
         <v>7538</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="10">
         <v>44710</v>
       </c>
@@ -28066,7 +28092,7 @@
         <v>7571</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="10">
         <v>44717</v>
       </c>
@@ -28101,7 +28127,7 @@
         <v>7788</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="10">
         <v>44724</v>
       </c>
@@ -28136,7 +28162,7 @@
         <v>7523</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="10">
         <v>44731</v>
       </c>
@@ -28171,7 +28197,7 @@
         <v>7309</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="10">
         <v>44738</v>
       </c>
@@ -28206,7 +28232,7 @@
         <v>7312</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="10">
         <v>44745</v>
       </c>
@@ -28241,7 +28267,7 @@
         <v>7701</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="10">
         <v>44752</v>
       </c>
@@ -28276,7 +28302,7 @@
         <v>7311</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="10">
         <v>44759</v>
       </c>
@@ -28311,7 +28337,7 @@
         <v>6911</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="10">
         <v>44766</v>
       </c>
@@ -28346,7 +28372,7 @@
         <v>6829</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="10">
         <v>44773</v>
       </c>
@@ -28381,7 +28407,7 @@
         <v>6597</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="10">
         <v>44780</v>
       </c>
@@ -28416,7 +28442,7 @@
         <v>6823</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="10">
         <v>44787</v>
       </c>
@@ -28451,7 +28477,7 @@
         <v>6785</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="10">
         <v>44794</v>
       </c>
@@ -28486,7 +28512,7 @@
         <v>6948</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="10">
         <v>44801</v>
       </c>
@@ -28521,7 +28547,7 @@
         <v>6759</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="10">
         <v>44808</v>
       </c>
@@ -28556,7 +28582,7 @@
         <v>6421</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="10">
         <v>44815</v>
       </c>
@@ -28591,7 +28617,7 @@
         <v>6562</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="10">
         <v>44822</v>
       </c>
@@ -28626,7 +28652,7 @@
         <v>6719</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="10">
         <v>44829</v>
       </c>
@@ -28661,7 +28687,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="10">
         <v>44836</v>
       </c>
@@ -28696,7 +28722,7 @@
         <v>5844</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="10">
         <v>44843</v>
       </c>
@@ -28731,7 +28757,7 @@
         <v>5551</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="10">
         <v>44850</v>
       </c>
@@ -28766,7 +28792,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="10">
         <v>44857</v>
       </c>
@@ -28801,7 +28827,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="10">
         <v>44864</v>
       </c>
@@ -28836,7 +28862,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="10">
         <v>44871</v>
       </c>
@@ -28871,7 +28897,7 @@
         <v>5488</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="10">
         <v>44878</v>
       </c>
@@ -28906,7 +28932,7 @@
         <v>5118</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="10">
         <v>44885</v>
       </c>
@@ -28941,7 +28967,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="10">
         <v>44892</v>
       </c>
@@ -28976,7 +29002,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="10">
         <v>44899</v>
       </c>
@@ -29011,7 +29037,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="10">
         <v>44906</v>
       </c>
@@ -29046,7 +29072,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="10">
         <v>44913</v>
       </c>
@@ -29081,7 +29107,7 @@
         <v>5665</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="10">
         <v>44920</v>
       </c>
@@ -29116,7 +29142,7 @@
         <v>5702</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="10">
         <v>44927</v>
       </c>
@@ -29151,7 +29177,7 @@
         <v>5586</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="10">
         <v>44934</v>
       </c>
@@ -29186,7 +29212,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="10">
         <v>44941</v>
       </c>
@@ -29221,7 +29247,7 @@
         <v>5141</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="10">
         <v>44948</v>
       </c>
@@ -29256,7 +29282,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="10">
         <v>44955</v>
       </c>
@@ -29291,7 +29317,7 @@
         <v>4191</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="10">
         <v>44962</v>
       </c>
@@ -29326,7 +29352,7 @@
         <v>4595</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="10">
         <v>44969</v>
       </c>
@@ -29361,7 +29387,7 @@
         <v>4305</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="10">
         <v>44976</v>
       </c>
@@ -29396,7 +29422,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="10">
         <v>44983</v>
       </c>
@@ -29431,7 +29457,7 @@
         <v>3701</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="10">
         <v>44990</v>
       </c>
@@ -29466,7 +29492,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="10">
         <v>44997</v>
       </c>
@@ -29501,7 +29527,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="10">
         <v>45004</v>
       </c>
@@ -29536,7 +29562,7 @@
         <v>4582</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="10">
         <v>45011</v>
       </c>
@@ -29571,7 +29597,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="10">
         <v>45018</v>
       </c>
@@ -29606,7 +29632,7 @@
         <v>4637</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="10">
         <v>45025</v>
       </c>
@@ -29641,7 +29667,7 @@
         <v>4417</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="10">
         <v>45032</v>
       </c>
@@ -29676,7 +29702,7 @@
         <v>4183</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="10">
         <v>45039</v>
       </c>
@@ -29711,7 +29737,7 @@
         <v>4090</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="10">
         <v>45046</v>
       </c>
@@ -29746,7 +29772,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="10">
         <v>45053</v>
       </c>
@@ -29781,7 +29807,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="10">
         <v>45060</v>
       </c>
@@ -29816,7 +29842,7 @@
         <v>3519</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="10">
         <v>45067</v>
       </c>
@@ -29851,7 +29877,7 @@
         <v>3513</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="10">
         <v>45074</v>
       </c>
@@ -29886,7 +29912,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="10">
         <v>45081</v>
       </c>
@@ -29921,7 +29947,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="10">
         <v>45088</v>
       </c>
@@ -29956,7 +29982,7 @@
         <v>3489</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="10">
         <v>45095</v>
       </c>
@@ -29991,7 +30017,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="10">
         <v>45102</v>
       </c>
@@ -30026,7 +30052,7 @@
         <v>3497</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="10">
         <v>45109</v>
       </c>
@@ -30061,7 +30087,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="10">
         <v>45116</v>
       </c>
@@ -30096,7 +30122,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="10">
         <v>45123</v>
       </c>
@@ -30131,7 +30157,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="10">
         <v>45130</v>
       </c>
@@ -30166,7 +30192,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="10">
         <v>45137</v>
       </c>
@@ -30201,7 +30227,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="10">
         <v>45144</v>
       </c>
@@ -30236,7 +30262,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="10">
         <v>45151</v>
       </c>
@@ -30271,7 +30297,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="10">
         <v>45158</v>
       </c>
@@ -30306,7 +30332,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="10">
         <v>45165</v>
       </c>
@@ -30341,7 +30367,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="10">
         <v>45172</v>
       </c>
@@ -30376,7 +30402,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="10">
         <v>45179</v>
       </c>
@@ -30411,7 +30437,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="10">
         <v>45186</v>
       </c>
@@ -30446,7 +30472,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="10">
         <v>45193</v>
       </c>
@@ -30481,7 +30507,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="10">
         <v>45200</v>
       </c>
@@ -30516,7 +30542,7 @@
         <v>4197</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="10">
         <v>45207</v>
       </c>
@@ -30551,7 +30577,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="10">
         <v>45214</v>
       </c>
@@ -30586,7 +30612,7 @@
         <v>4268</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="10">
         <v>45221</v>
       </c>
@@ -30621,7 +30647,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="10">
         <v>45228</v>
       </c>
@@ -30656,7 +30682,7 @@
         <v>4465</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="10">
         <v>45235</v>
       </c>
@@ -30691,7 +30717,7 @@
         <v>4486</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="10">
         <v>45242</v>
       </c>
@@ -30726,7 +30752,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="10">
         <v>45249</v>
       </c>
@@ -30761,7 +30787,7 @@
         <v>5136</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="10">
         <v>45256</v>
       </c>
@@ -30796,7 +30822,7 @@
         <v>5562</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="10">
         <v>45263</v>
       </c>
@@ -30831,7 +30857,7 @@
         <v>5625</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="10">
         <v>45270</v>
       </c>
@@ -30866,7 +30892,7 @@
         <v>5859</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="10">
         <v>45277</v>
       </c>
@@ -30901,7 +30927,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="10">
         <v>45284</v>
       </c>
@@ -30936,7 +30962,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="10">
         <v>45291</v>
       </c>
@@ -30971,7 +30997,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="10">
         <v>45298</v>
       </c>
@@ -31006,7 +31032,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="10">
         <v>45305</v>
       </c>
@@ -31041,7 +31067,7 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="10">
         <v>45312</v>
       </c>
@@ -31076,7 +31102,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="10">
         <v>45319</v>
       </c>
@@ -31111,7 +31137,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="10">
         <v>45326</v>
       </c>
@@ -31146,7 +31172,7 @@
         <v>4283</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="10">
         <v>45333</v>
       </c>
@@ -31181,7 +31207,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="10">
         <v>45340</v>
       </c>
@@ -31216,7 +31242,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="10">
         <v>45347</v>
       </c>
@@ -31251,7 +31277,7 @@
         <v>3455</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="10">
         <v>45354</v>
       </c>
@@ -31286,7 +31312,7 @@
         <v>3638</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="10">
         <v>45361</v>
       </c>
@@ -31321,7 +31347,7 @@
         <v>3888</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="10">
         <v>45368</v>
       </c>
@@ -31356,7 +31382,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="10">
         <v>45375</v>
       </c>
@@ -31391,7 +31417,7 @@
         <v>4396</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="10">
         <v>45382</v>
       </c>
@@ -31426,7 +31452,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="10">
         <v>45389</v>
       </c>
@@ -31461,7 +31487,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="10">
         <v>45396</v>
       </c>
@@ -31496,7 +31522,7 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="10">
         <v>45403</v>
       </c>
@@ -31531,7 +31557,7 @@
         <v>4580</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="10">
         <v>45410</v>
       </c>
@@ -31566,7 +31592,7 @@
         <v>4632</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="10">
         <v>45417</v>
       </c>
@@ -31601,7 +31627,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="10">
         <v>45424</v>
       </c>
@@ -31636,7 +31662,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="10">
         <v>45431</v>
       </c>
@@ -31671,7 +31697,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="10">
         <v>45438</v>
       </c>
@@ -31706,7 +31732,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="10">
         <v>45445</v>
       </c>
@@ -31741,7 +31767,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="10">
         <v>45452</v>
       </c>
@@ -31776,7 +31802,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="10">
         <v>45459</v>
       </c>
@@ -31811,7 +31837,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="10">
         <v>45466</v>
       </c>
@@ -31846,7 +31872,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="10">
         <v>45473</v>
       </c>
@@ -31881,7 +31907,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="10">
         <v>45480</v>
       </c>
@@ -31916,7 +31942,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="10">
         <v>45487</v>
       </c>
@@ -31951,7 +31977,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="10">
         <v>45494</v>
       </c>
@@ -31986,7 +32012,7 @@
         <v>4594</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="10">
         <v>45501</v>
       </c>
@@ -32021,7 +32047,7 @@
         <v>4598</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="10">
         <v>45508</v>
       </c>
@@ -32056,7 +32082,7 @@
         <v>4565</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="10">
         <v>45515</v>
       </c>
@@ -32091,7 +32117,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="10">
         <v>45522</v>
       </c>
@@ -32126,7 +32152,7 @@
         <v>4591</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="10">
         <v>45529</v>
       </c>
@@ -32161,7 +32187,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="10">
         <v>45536</v>
       </c>
@@ -32196,7 +32222,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="10">
         <v>45543</v>
       </c>
@@ -32231,7 +32257,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="10">
         <v>45550</v>
       </c>
@@ -32266,7 +32292,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="10">
         <v>45557</v>
       </c>
@@ -32301,7 +32327,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="10">
         <v>45564</v>
       </c>
@@ -32336,7 +32362,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="10">
         <v>45571</v>
       </c>
@@ -32371,7 +32397,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="10">
         <v>45578</v>
       </c>
@@ -32406,7 +32432,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="10">
         <v>45585</v>
       </c>
@@ -32441,7 +32467,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="10">
         <v>45592</v>
       </c>
@@ -32476,7 +32502,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="10">
         <v>45599</v>
       </c>
@@ -32511,7 +32537,7 @@
         <v>5493</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="10">
         <v>45606</v>
       </c>
@@ -32546,7 +32572,7 @@
         <v>5494</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="10">
         <v>45613</v>
       </c>
@@ -32581,7 +32607,7 @@
         <v>5339</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="10">
         <v>45620</v>
       </c>
@@ -32616,7 +32642,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="10">
         <v>45627</v>
       </c>
@@ -32651,7 +32677,7 @@
         <v>5585</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="10">
         <v>45634</v>
       </c>
@@ -32686,7 +32712,7 @@
         <v>5777</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="10">
         <v>45641</v>
       </c>
@@ -32721,7 +32747,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="10">
         <v>45648</v>
       </c>
@@ -32756,7 +32782,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="10">
         <v>45655</v>
       </c>
@@ -32791,7 +32817,7 @@
         <v>5327</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="10">
         <v>45662</v>
       </c>
@@ -32826,7 +32852,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="10">
         <v>45669</v>
       </c>
@@ -32861,7 +32887,7 @@
         <v>4484</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="10">
         <v>45676</v>
       </c>
@@ -32896,7 +32922,7 @@
         <v>4243</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="10">
         <v>45683</v>
       </c>
@@ -32931,7 +32957,7 @@
         <v>4447</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="10">
         <v>45690</v>
       </c>
@@ -32966,7 +32992,7 @@
         <v>4327</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="10">
         <v>45697</v>
       </c>
@@ -33001,7 +33027,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="10">
         <v>45704</v>
       </c>
@@ -33036,7 +33062,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="10">
         <v>45711</v>
       </c>
@@ -33071,7 +33097,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="10">
         <v>45718</v>
       </c>
@@ -33106,7 +33132,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="10">
         <v>45725</v>
       </c>
@@ -33141,7 +33167,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="10">
         <v>45732</v>
       </c>
@@ -33176,7 +33202,7 @@
         <v>4218</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="10">
         <v>45739</v>
       </c>
@@ -33211,7 +33237,7 @@
         <v>4547</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="10">
         <v>45746</v>
       </c>
@@ -33246,7 +33272,7 @@
         <v>4573</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="10">
         <v>45753</v>
       </c>
@@ -33281,7 +33307,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="10">
         <v>45760</v>
       </c>
@@ -33316,7 +33342,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="10">
         <v>45767</v>
       </c>
@@ -33351,7 +33377,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="10">
         <v>45774</v>
       </c>
@@ -33386,7 +33412,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="10">
         <v>45781</v>
       </c>
@@ -33421,7 +33447,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="10">
         <v>45788</v>
       </c>
@@ -33456,7 +33482,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="10">
         <v>45795</v>
       </c>
@@ -33491,7 +33517,7 @@
         <v>4190</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="10">
         <v>45802</v>
       </c>
@@ -33526,7 +33552,7 @@
         <v>4444</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="10">
         <v>45809</v>
       </c>
@@ -33561,7 +33587,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="10">
         <v>45816</v>
       </c>
@@ -33596,7 +33622,7 @@
         <v>4567</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="10">
         <v>45823</v>
       </c>
@@ -33631,7 +33657,7 @@
         <v>4475</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="10">
         <v>45830</v>
       </c>
@@ -33666,7 +33692,7 @@
         <v>4354</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="10">
         <v>45837</v>
       </c>
@@ -33701,7 +33727,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="10">
         <v>45844</v>
       </c>
@@ -33736,7 +33762,7 @@
         <v>4413</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="10">
         <v>45851</v>
       </c>
@@ -33771,7 +33797,7 @@
         <v>4593</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="10">
         <v>45858</v>
       </c>
@@ -33806,7 +33832,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="10">
         <v>45865</v>
       </c>
@@ -33841,7 +33867,7 @@
         <v>4429</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="10">
         <v>45872</v>
       </c>
@@ -33876,7 +33902,7 @@
         <v>4418</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="10">
         <v>45879</v>
       </c>
@@ -33911,7 +33937,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="10">
         <v>45886</v>
       </c>
@@ -33946,7 +33972,7 @@
         <v>4411</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="10">
         <v>45893</v>
       </c>
@@ -33981,7 +34007,7 @@
         <v>4392</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="10">
         <v>45900</v>
       </c>
@@ -34016,7 +34042,7 @@
         <v>4549</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="10">
         <v>45907</v>
       </c>
@@ -34051,7 +34077,7 @@
         <v>4489</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="10">
         <v>45914</v>
       </c>
@@ -34086,7 +34112,7 @@
         <v>4536</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="10">
         <v>45921</v>
       </c>
@@ -34121,7 +34147,7 @@
         <v>4516</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="10">
         <v>45928</v>
       </c>
@@ -34156,7 +34182,7 @@
         <v>4562</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="10">
         <v>45935</v>
       </c>
@@ -34191,7 +34217,7 @@
         <v>4621</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="10">
         <v>45942</v>
       </c>
@@ -34226,7 +34252,7 @@
         <v>4441</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="10">
         <v>45949</v>
       </c>
@@ -34261,7 +34287,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="10">
         <v>45956</v>
       </c>
@@ -34296,7 +34322,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="10">
         <v>45963</v>
       </c>
@@ -34331,7 +34357,7 @@
         <v>5366</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="10">
         <v>45970</v>
       </c>
@@ -34366,7 +34392,7 @@
         <v>5356</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="10">
         <v>45977</v>
       </c>
@@ -34401,7 +34427,7 @@
         <v>5581</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="10">
         <v>45984</v>
       </c>
@@ -34436,7 +34462,7 @@
         <v>5571</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="10">
         <v>45991</v>
       </c>
@@ -34471,7 +34497,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="10">
         <v>45998</v>
       </c>
@@ -34506,7 +34532,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="10">
         <v>46005</v>
       </c>
@@ -34541,7 +34567,7 @@
         <v>6369</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="10">
         <v>46012</v>
       </c>
@@ -34576,7 +34602,7 @@
         <v>5821</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="10">
         <v>46026</v>
       </c>
@@ -34611,7 +34637,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="10">
         <v>46033</v>
       </c>
@@ -34646,7 +34672,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="10">
         <v>46040</v>
       </c>
@@ -34681,7 +34707,7 @@
         <v>4558</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="10">
         <v>46047</v>
       </c>
@@ -34716,7 +34742,7 @@
         <v>4478</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="10">
         <v>46054</v>
       </c>
@@ -34751,7 +34777,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="10">
         <v>46061</v>
       </c>
@@ -34786,7 +34812,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="10">
         <v>46068</v>
       </c>
@@ -34821,7 +34847,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" s="10">
         <v>46075</v>
       </c>
@@ -34856,7 +34882,7 @@
         <v>4432</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" s="10">
         <v>46082</v>
       </c>
@@ -34891,7 +34917,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="10">
         <v>46089</v>
       </c>
@@ -34926,7 +34952,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" s="10">
         <v>46096</v>
       </c>
@@ -34961,7 +34987,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" s="10">
         <v>46103</v>
       </c>
@@ -34996,7 +35022,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" s="10">
         <v>46110</v>
       </c>
@@ -35029,6 +35055,20 @@
       </c>
       <c r="K432" s="9">
         <v>5348</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A433" s="10">
+        <v>46117</v>
+      </c>
+      <c r="B433" s="8">
+        <v>46118</v>
+      </c>
+      <c r="C433" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D433" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -35047,7 +35087,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35062,12 +35102,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -35079,7 +35119,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4285A59-043C-45FB-ABA0-B72EFC951D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29BFEA9-E799-4BF6-A1BD-62857BAB0C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1648,6 +1645,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2949,6 +2949,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>2519</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>2555</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4288,6 +4291,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5589,6 +5595,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>1173</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6928,6 +6937,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8229,6 +8241,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>4205</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9568,6 +9583,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10869,6 +10887,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>1292</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12208,6 +12229,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13509,6 +13533,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>1192</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14850,6 +14877,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16151,6 +16181,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>5689</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>5631</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17506,6 +17539,9 @@
                 <c:pt idx="430">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="431">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -18807,6 +18843,9 @@
                 </c:pt>
                 <c:pt idx="430">
                   <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19050,6 +19089,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -19057,7 +19097,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -19952,16 +19991,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K433"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K434"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.09765625" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
@@ -35111,6 +35150,41 @@
       </c>
       <c r="K433" s="9">
         <v>5689</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A434" s="10">
+        <v>46124</v>
+      </c>
+      <c r="B434" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C434" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D434" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E434" s="9">
+        <v>2555</v>
+      </c>
+      <c r="F434" s="9">
+        <v>1157</v>
+      </c>
+      <c r="G434" s="9">
+        <v>4345</v>
+      </c>
+      <c r="H434" s="9">
+        <v>1474</v>
+      </c>
+      <c r="I434" s="9">
+        <v>1127</v>
+      </c>
+      <c r="J434" s="9">
+        <v>300</v>
+      </c>
+      <c r="K434" s="9">
+        <v>5631</v>
       </c>
     </row>
   </sheetData>
@@ -35129,7 +35203,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35144,12 +35218,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
@@ -35161,7 +35235,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818B1256-E9FD-4242-8C8E-C10AE7EC1445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB7FBF-02A3-423A-AD88-C172A724DC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="25">
   <si>
     <t>Shanghai Pudong Outbound</t>
   </si>
@@ -1663,6 +1663,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2982,6 +2985,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>2614</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>2608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4339,6 +4345,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5658,6 +5667,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>1075</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7015,6 +7027,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8334,6 +8349,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>4592</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4552</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9691,6 +9709,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11010,6 +11031,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>1190</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1155</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12367,6 +12391,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13686,6 +13713,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>1303</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15045,6 +15075,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16364,6 +16397,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>5807</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>5932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17737,6 +17773,9 @@
                 <c:pt idx="436">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="437">
+                  <c:v>46167</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19056,6 +19095,9 @@
                 </c:pt>
                 <c:pt idx="436">
                   <c:v>341</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20202,7 +20244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K439"/>
+  <dimension ref="A1:K440"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="10" bestFit="1" customWidth="1"/>
@@ -35571,6 +35613,41 @@
       </c>
       <c r="K439" s="9">
         <v>5807</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11">
+      <c r="A440" s="10">
+        <v>46166</v>
+      </c>
+      <c r="B440" s="8">
+        <v>46167</v>
+      </c>
+      <c r="C440" s="11">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D440" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E440" s="9">
+        <v>2608</v>
+      </c>
+      <c r="F440" s="9">
+        <v>1157</v>
+      </c>
+      <c r="G440" s="9">
+        <v>4552</v>
+      </c>
+      <c r="H440" s="9">
+        <v>1155</v>
+      </c>
+      <c r="I440" s="9">
+        <v>1135</v>
+      </c>
+      <c r="J440" s="9">
+        <v>360</v>
+      </c>
+      <c r="K440" s="9">
+        <v>5932</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B92C3D-1AF9-4A6A-99E9-84081B3DD41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E84A9B-66B7-4044-BAB4-EA066CF97A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAI" sheetId="1" r:id="rId1"/>
@@ -280,9 +280,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -300,7 +300,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2998,10 +2998,13 @@
                 <c:pt idx="438">
                   <c:v>2680</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>2679</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -5689,10 +5692,13 @@
                 <c:pt idx="438">
                   <c:v>1055</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>1088</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -8380,10 +8386,13 @@
                 <c:pt idx="438">
                   <c:v>4735</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>4673</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -11071,6 +11080,9 @@
                 <c:pt idx="438">
                   <c:v>1520</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>1235</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13762,10 +13774,13 @@
                 <c:pt idx="438">
                   <c:v>1161</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>1307</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -16455,10 +16470,13 @@
                 <c:pt idx="438">
                   <c:v>5984</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>6121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -19162,10 +19180,13 @@
                 <c:pt idx="438">
                   <c:v>261</c:v>
                 </c:pt>
+                <c:pt idx="439">
+                  <c:v>211</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-C218-4013-AFF2-EEEFCF8C2C0B}"/>
@@ -20308,16 +20329,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K442"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.90625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" style="8" customWidth="1"/>
-    <col min="5" max="8" width="8.54296875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="8" customWidth="1"/>
+    <col min="5" max="8" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -35760,6 +35781,27 @@
       </c>
       <c r="D442" s="8" t="s">
         <v>22</v>
+      </c>
+      <c r="E442" s="9">
+        <v>2679</v>
+      </c>
+      <c r="F442" s="9">
+        <v>1088</v>
+      </c>
+      <c r="G442" s="9">
+        <v>4673</v>
+      </c>
+      <c r="H442" s="9">
+        <v>1235</v>
+      </c>
+      <c r="I442" s="9">
+        <v>1307</v>
+      </c>
+      <c r="J442" s="9">
+        <v>211</v>
+      </c>
+      <c r="K442" s="9">
+        <v>6121</v>
       </c>
     </row>
   </sheetData>
@@ -35779,7 +35821,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49EC86-403A-4933-BA0C-EED828B128BC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="12"/>
   </cols>
@@ -35795,12 +35837,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362BE34E-9F1D-4DC0-8A14-D289984A66A9}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16">
+    <row r="2" spans="2:7" ht="15.6">
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>

--- a/data/freight/Baltic air freight index.xlsx
+++ b/data/freight/Baltic air freight index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D150B09B-F3FA-40C6-87C0-C6AF0F39136E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2785CCEF-BBF5-4201-A679-E7512476A6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="18">
   <si>
     <t>BAI80</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1648,6 +1648,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2982,6 +2985,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>2760</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>2623</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4351,6 +4357,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5685,6 +5694,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>1222</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7054,6 +7066,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8388,6 +8403,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>4758</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4442</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9757,6 +9775,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11091,6 +11112,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>1270</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12460,6 +12484,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13794,6 +13821,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>1316</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1225</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15165,6 +15195,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16499,6 +16532,9 @@
                 </c:pt>
                 <c:pt idx="441">
                   <c:v>6239</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>5992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17884,6 +17920,9 @@
                 <c:pt idx="441">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="442">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19217,6 +19256,9 @@
                   <c:v>234</c:v>
                 </c:pt>
                 <c:pt idx="441">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="442">
                   <c:v>282</c:v>
                 </c:pt>
               </c:numCache>
@@ -20364,7 +20406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K443"/>
+  <dimension ref="A1:K444"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -35878,6 +35920,41 @@
       </c>
       <c r="K443" s="13">
         <v>6239</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11">
+      <c r="A444" s="10">
+        <v>46201</v>
+      </c>
+      <c r="B444" s="11">
+        <v>46202</v>
+      </c>
+      <c r="C444" s="12">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D444" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E444" s="13">
+        <v>2623</v>
+      </c>
+      <c r="F444" s="13">
+        <v>1206</v>
+      </c>
+      <c r="G444" s="13">
+        <v>4442</v>
+      </c>
+      <c r="H444" s="13">
+        <v>1203</v>
+      </c>
+      <c r="I444" s="13">
+        <v>1225</v>
+      </c>
+      <c r="J444" s="13">
+        <v>282</v>
+      </c>
+      <c r="K444" s="13">
+        <v>5992</v>
       </c>
     </row>
   </sheetData>
